--- a/data/trans_orig/P57B5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido rebosante de energía en 2023</t>
+          <t>Población según se ha sentido rebosante de energía en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>187333</t>
+          <t>184351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>230516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155969</t>
+          <t>155736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193490</t>
+          <t>191289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354855</t>
+          <t>354790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>413301</t>
+          <t>411507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184453</t>
+          <t>187165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231029</t>
+          <t>232725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168178</t>
+          <t>170273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203286</t>
+          <t>205409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367043</t>
+          <t>369585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425206</t>
+          <t>425821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51492</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>54055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>79495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>113646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151531</t>
+          <t>151729</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35352</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>29278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>158692</t>
+          <t>161202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>203230</t>
+          <t>205283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105111</t>
+          <t>104749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138325</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>278270</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>331519</t>
+          <t>329438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219791</t>
+          <t>218838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155823</t>
+          <t>157627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190044</t>
+          <t>190359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>342665</t>
+          <t>342421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397888</t>
+          <t>397913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47988</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76644</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90045</t>
+          <t>89096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117197</t>
+          <t>115927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155992</t>
+          <t>154230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286726</t>
+          <t>287287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575524</t>
+          <t>573018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332287</t>
+          <t>330999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688057</t>
+          <t>689144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57967</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>248034</t>
+          <t>249186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79917</t>
+          <t>79411</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88136</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>319148</t>
+          <t>321843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>112931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43575</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150235</t>
+          <t>151577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42156</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>356334</t>
+          <t>353062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>427320</t>
+          <t>427591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>121032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>309758</t>
+          <t>311089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>429304</t>
+          <t>429477</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>714144</t>
+          <t>714233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>379584</t>
+          <t>373683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>447785</t>
+          <t>444715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>420341</t>
+          <t>418180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>745942</t>
+          <t>762169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>821207</t>
+          <t>822684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1304440</t>
+          <t>1271702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162907</t>
+          <t>161461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212713</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77070</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194945</t>
+          <t>194721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>235584</t>
+          <t>240260</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>387032</t>
+          <t>384681</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55384</t>
+          <t>56444</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63876</t>
+          <t>64305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107429</t>
+          <t>108172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133679</t>
+          <t>132936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>179448</t>
+          <t>175881</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135312</t>
+          <t>135905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210937</t>
+          <t>213693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>280015</t>
+          <t>276319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377801</t>
+          <t>377056</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168327</t>
+          <t>165948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>211816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351407</t>
+          <t>348840</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>518168</t>
+          <t>516366</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>533179</t>
+          <t>531912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>727354</t>
+          <t>728465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79691</t>
+          <t>79446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114833</t>
+          <t>112837</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130774</t>
+          <t>131127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>202687</t>
+          <t>203354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>218383</t>
+          <t>219410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>298834</t>
+          <t>302471</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27770</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>50659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>93419</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>89179</t>
+          <t>89846</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133841</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>125854</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>174943</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>214597</t>
+          <t>214113</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>266153</t>
+          <t>265302</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>354714</t>
+          <t>350794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>433018</t>
+          <t>430556</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>45306</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>92670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261801</t>
+          <t>261028</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>311918</t>
+          <t>311143</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319186</t>
+          <t>321119</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>390895</t>
+          <t>391122</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>154278</t>
+          <t>156316</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>194555</t>
+          <t>195025</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>170274</t>
+          <t>168142</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>215813</t>
+          <t>215805</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>67831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46518</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>70433</t>
+          <t>71406</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1353105</t>
+          <t>1355613</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1953547</t>
+          <t>2002616</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>833140</t>
+          <t>821140</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1096666</t>
+          <t>1100702</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2297529</t>
+          <t>2283801</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3087249</t>
+          <t>2957632</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>938891</t>
+          <t>931152</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1344822</t>
+          <t>1343786</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1518761</t>
+          <t>1510311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1990546</t>
+          <t>2002906</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2620142</t>
+          <t>2610813</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3261649</t>
+          <t>3239888</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>388546</t>
+          <t>369917</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>550893</t>
+          <t>547763</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>553123</t>
+          <t>558511</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>728853</t>
+          <t>734957</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1004797</t>
+          <t>1012767</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1262762</t>
+          <t>1258062</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>158848</t>
+          <t>158483</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>183328</t>
+          <t>182286</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>250817</t>
+          <t>249426</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>300261</t>
+          <t>302980</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>392897</t>
+          <t>395004</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>207827</t>
+          <t>232477</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>184351</t>
+          <t>207945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>230516</t>
+          <t>258233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>174511</t>
+          <t>188023</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155736</t>
+          <t>170568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191289</t>
+          <t>209263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>382338</t>
+          <t>420501</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354790</t>
+          <t>389595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>411507</t>
+          <t>450877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>208885</t>
+          <t>224186</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187165</t>
+          <t>200122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>232725</t>
+          <t>246208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>186072</t>
+          <t>204323</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170273</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205409</t>
+          <t>223975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>394957</t>
+          <t>428509</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>369585</t>
+          <t>397667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425821</t>
+          <t>459831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65957</t>
+          <t>70455</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52836</t>
+          <t>55215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80812</t>
+          <t>86321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65997</t>
+          <t>74617</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54055</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79495</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>131954</t>
+          <t>145072</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>126086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151729</t>
+          <t>165607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42888</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>550023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952137</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>182775</t>
+          <t>198471</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161202</t>
+          <t>177975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205283</t>
+          <t>222093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120483</t>
+          <t>134680</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104749</t>
+          <t>117668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136471</t>
+          <t>151727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>303259</t>
+          <t>333151</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>306228</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>329438</t>
+          <t>363777</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>197334</t>
+          <t>208879</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174290</t>
+          <t>186725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218838</t>
+          <t>231586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>188503</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157627</t>
+          <t>171284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190359</t>
+          <t>205426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>370815</t>
+          <t>397383</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>342421</t>
+          <t>367497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>426418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61306</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48715</t>
+          <t>50653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77332</t>
+          <t>81836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74588</t>
+          <t>83143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>96989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>135895</t>
+          <t>147495</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115927</t>
+          <t>127670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154230</t>
+          <t>170233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>432840</t>
+          <t>210395</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287287</t>
+          <t>187809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573018</t>
+          <t>231092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>70835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>485320</t>
+          <t>270005</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330999</t>
+          <t>243405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>689144</t>
+          <t>293758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>151721</t>
+          <t>171642</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61170</t>
+          <t>150871</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>249186</t>
+          <t>193609</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69307</t>
+          <t>78344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59096</t>
+          <t>66823</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79411</t>
+          <t>90697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>221028</t>
+          <t>249987</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>226364</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>321843</t>
+          <t>274730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66787</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112931</t>
+          <t>89159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>110030</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>94221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151577</t>
+          <t>129262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667602</t>
+          <t>470878</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667602</t>
+          <t>470878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667602</t>
+          <t>470878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166187</t>
+          <t>186768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>833789</t>
+          <t>657646</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>833789</t>
+          <t>657646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>833789</t>
+          <t>657646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>390327</t>
+          <t>426051</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>353062</t>
+          <t>390385</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>427591</t>
+          <t>463246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>237880</t>
+          <t>264896</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121032</t>
+          <t>241379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>311089</t>
+          <t>290817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>628207</t>
+          <t>690947</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>429477</t>
+          <t>647264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>714233</t>
+          <t>737151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>411945</t>
+          <t>455244</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>373683</t>
+          <t>417273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>444715</t>
+          <t>490682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>542877</t>
+          <t>375777</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>418180</t>
+          <t>351446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>762169</t>
+          <t>403667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>954821</t>
+          <t>831021</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>822684</t>
+          <t>784249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1271702</t>
+          <t>876650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>187142</t>
+          <t>201707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>161461</t>
+          <t>179739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>226766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148650</t>
+          <t>166775</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73318</t>
+          <t>148310</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194721</t>
+          <t>185526</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335791</t>
+          <t>368482</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>240260</t>
+          <t>337992</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>384681</t>
+          <t>401743</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>45777</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32588</t>
+          <t>34764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46402</t>
+          <t>51361</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>62749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88942</t>
+          <t>97138</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>80855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108172</t>
+          <t>115734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1031954</t>
+          <t>1128780</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1031954</t>
+          <t>1128780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1031954</t>
+          <t>1128780</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>975809</t>
+          <t>858808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>975809</t>
+          <t>858808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>975809</t>
+          <t>858808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2007762</t>
+          <t>1987588</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2007762</t>
+          <t>1987588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2007762</t>
+          <t>1987588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>154161</t>
+          <t>183189</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132936</t>
+          <t>157286</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>175881</t>
+          <t>206934</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>181751</t>
+          <t>205458</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135905</t>
+          <t>184877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>213693</t>
+          <t>225314</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>335912</t>
+          <t>388647</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276319</t>
+          <t>357830</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377056</t>
+          <t>423636</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>187859</t>
+          <t>233252</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165948</t>
+          <t>209129</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211816</t>
+          <t>262726</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>407989</t>
+          <t>352260</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348840</t>
+          <t>328064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>516366</t>
+          <t>376247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>595848</t>
+          <t>585512</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>531912</t>
+          <t>550238</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>728465</t>
+          <t>618850</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>95833</t>
+          <t>109301</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79446</t>
+          <t>92461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112837</t>
+          <t>129331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>174298</t>
+          <t>194230</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131127</t>
+          <t>174841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203354</t>
+          <t>215327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>270131</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>219410</t>
+          <t>277794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>302471</t>
+          <t>329833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37192</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50659</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>63489</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>88463</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>111739</t>
+          <t>118284</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>89846</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133590</t>
+          <t>139290</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838584</t>
+          <t>828009</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838584</t>
+          <t>828009</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838584</t>
+          <t>828009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313630</t>
+          <t>1395973</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313630</t>
+          <t>1395973</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313630</t>
+          <t>1395973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>151854</t>
+          <t>156587</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125854</t>
+          <t>134503</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174943</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>240279</t>
+          <t>271164</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>214113</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>265302</t>
+          <t>299854</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>392133</t>
+          <t>427750</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>350794</t>
+          <t>389873</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>430556</t>
+          <t>464611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>68444</t>
+          <t>60709</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92670</t>
+          <t>83135</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>285712</t>
+          <t>321148</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261028</t>
+          <t>294833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>311143</t>
+          <t>349088</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>354156</t>
+          <t>381856</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>321119</t>
+          <t>350962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>391122</t>
+          <t>418998</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>173949</t>
+          <t>188186</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>167746</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>195025</t>
+          <t>209059</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>191330</t>
+          <t>205430</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>168142</t>
+          <t>182715</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>215805</t>
+          <t>230983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>55566</t>
+          <t>59813</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>46102</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67831</t>
+          <t>71805</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>57862</t>
+          <t>61986</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>71406</t>
+          <t>75533</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>239975</t>
+          <t>236712</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>239975</t>
+          <t>236712</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>239975</t>
+          <t>236712</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>755506</t>
+          <t>840311</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>755506</t>
+          <t>840311</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>755506</t>
+          <t>840311</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>995481</t>
+          <t>1077022</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>995481</t>
+          <t>1077022</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>995481</t>
+          <t>1077022</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1519784</t>
+          <t>1407170</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1355613</t>
+          <t>1340853</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2002616</t>
+          <t>1474378</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1007386</t>
+          <t>1123831</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>821140</t>
+          <t>1070741</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1100702</t>
+          <t>1178450</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2527170</t>
+          <t>2531001</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2283801</t>
+          <t>2449477</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2957632</t>
+          <t>2621341</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1226188</t>
+          <t>1353912</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>931152</t>
+          <t>1284362</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1343786</t>
+          <t>1416267</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1665437</t>
+          <t>1520355</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1510311</t>
+          <t>1467662</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2002906</t>
+          <t>1573423</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2891625</t>
+          <t>2874268</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2610813</t>
+          <t>2789687</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3239888</t>
+          <t>2964736</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>494407</t>
+          <t>535108</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>369917</t>
+          <t>493445</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>547763</t>
+          <t>584133</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>671861</t>
+          <t>744932</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>558511</t>
+          <t>708927</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>734957</t>
+          <t>788217</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1166268</t>
+          <t>1280040</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1012767</t>
+          <t>1219481</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1258062</t>
+          <t>1342466</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>131080</t>
+          <t>141379</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>158483</t>
+          <t>165451</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>221449</t>
+          <t>236331</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>182286</t>
+          <t>213319</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>249426</t>
+          <t>258604</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>352529</t>
+          <t>377710</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>302980</t>
+          <t>346663</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>415468</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3371459</t>
+          <t>3437569</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3371459</t>
+          <t>3437569</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3371459</t>
+          <t>3437569</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3566133</t>
+          <t>3625450</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3566133</t>
+          <t>3625450</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3566133</t>
+          <t>3625450</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6937592</t>
+          <t>7063019</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6937592</t>
+          <t>7063019</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6937592</t>
+          <t>7063019</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
